--- a/artfynd/A 30317-2026 artfynd.xlsx
+++ b/artfynd/A 30317-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -796,6 +801,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135473483</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -903,8 +913,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135474938</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 30317-2026 artfynd.xlsx
+++ b/artfynd/A 30317-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135473483</v>
       </c>
       <c r="B2" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         <v>135474938</v>
       </c>
       <c r="B3" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 30317-2026 artfynd.xlsx
+++ b/artfynd/A 30317-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135473483</v>
       </c>
       <c r="B2" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         <v>135474938</v>
       </c>
       <c r="B3" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 30317-2026 artfynd.xlsx
+++ b/artfynd/A 30317-2026 artfynd.xlsx
@@ -812,7 +812,7 @@
         <v>135741780</v>
       </c>
       <c r="B3" t="n">
-        <v>92459</v>
+        <v>92461</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>135742534</v>
       </c>
       <c r="B7" t="n">
-        <v>98295</v>
+        <v>98297</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>135742392</v>
       </c>
       <c r="B8" t="n">
-        <v>106411</v>
+        <v>106413</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 30317-2026 artfynd.xlsx
+++ b/artfynd/A 30317-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ8"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135473483</v>
+        <v>136037267</v>
       </c>
       <c r="B2" t="n">
-        <v>79107</v>
+        <v>97529</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,45 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Röberga, Röberga, Ög</t>
+          <t>Röberga, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556155</v>
+        <v>556083</v>
       </c>
       <c r="R2" t="n">
-        <v>6432477</v>
+        <v>6432676</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,27 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:01</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:01</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Några dm3 på två olika talllågor som låg nära varandra.</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,56 +759,55 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Linnea Druid</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Linnea Druid, Henrik Druid</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135473483</t>
+          <t>https://artportalen.se/Sighting/136037267</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135741780</v>
+        <v>136037315</v>
       </c>
       <c r="B3" t="n">
-        <v>92461</v>
+        <v>97529</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5420</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -844,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556056</v>
+        <v>556096</v>
       </c>
       <c r="R3" t="n">
-        <v>6432617</v>
+        <v>6432665</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,12 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,22 +872,22 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Hugo Axelsson, Hasse Andersson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135741780</t>
+          <t>https://artportalen.se/Sighting/136037315</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135474938</v>
+        <v>135473483</v>
       </c>
       <c r="B4" t="n">
-        <v>80060</v>
+        <v>79107</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -922,24 +895,35 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Röberga, Röberga, Ög</t>
@@ -981,7 +965,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -991,7 +975,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Några dm3 på två olika talllågor som låg nära varandra.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1000,6 +989,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1011,44 +1001,44 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Linnea Druid</t>
+          <t>Linnea Druid, Henrik Druid</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135474938</t>
+          <t>https://artportalen.se/Sighting/135473483</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135741743</v>
+        <v>136037172</v>
       </c>
       <c r="B5" t="n">
-        <v>80060</v>
+        <v>79637</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>1639</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blomskägglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Usnea florida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Weber ex F.H.Wigg.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1058,13 +1048,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556056</v>
+        <v>556083</v>
       </c>
       <c r="R5" t="n">
-        <v>6432617</v>
+        <v>6432690</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1088,12 +1078,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,44 +1103,44 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Hugo Axelsson, Hasse Andersson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135741743</t>
+          <t>https://artportalen.se/Sighting/136037172</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135742592</v>
+        <v>136037509</v>
       </c>
       <c r="B6" t="n">
-        <v>5497</v>
+        <v>79637</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>101410</v>
+        <v>1639</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Blomskägglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Usnea florida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(L.) Weber ex F.H.Wigg.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1160,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555977</v>
+        <v>556096</v>
       </c>
       <c r="R6" t="n">
-        <v>6432526</v>
+        <v>6432665</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,12 +1180,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,22 +1205,22 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Hugo Axelsson, Hasse Andersson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135742592</t>
+          <t>https://artportalen.se/Sighting/136037509</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135742534</v>
+        <v>136037006</v>
       </c>
       <c r="B7" t="n">
-        <v>98297</v>
+        <v>96595</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1238,37 +1228,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219815</v>
+        <v>2671</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Röberga, Röberga, Ög</t>
+          <t>Röberga, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555984</v>
+        <v>556066</v>
       </c>
       <c r="R7" t="n">
-        <v>6432565</v>
+        <v>6432690</v>
       </c>
       <c r="S7" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1292,22 +1282,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>14:39</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:39</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1322,27 +1302,27 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Hasse Andersson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Hasse Andersson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135742534</t>
+          <t>https://artportalen.se/Sighting/136037006</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135742392</v>
+        <v>135741780</v>
       </c>
       <c r="B8" t="n">
-        <v>106413</v>
+        <v>92461</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1350,41 +1330,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>5420</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Röberga, Röberga, Ög</t>
+          <t>Röberga, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>556022</v>
+        <v>556056</v>
       </c>
       <c r="R8" t="n">
-        <v>6432559</v>
+        <v>6432617</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1411,44 +1387,1101 @@
           <t>2026-08-08</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>14:35</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-08-08</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>14:35</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Hasse Andersson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Hasse Andersson, Rebecca Wikström, Hugo Axelsson, Emma Nordenberg</t>
+          <t>Emma Nordenberg, Hugo Axelsson, Hasse Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135741780</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136038484</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92022</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5445</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ekticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Fomitiporia robusta</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Röberga, Ög</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>556016</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6432539</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Oppeby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136038484</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135474938</v>
+      </c>
+      <c r="B10" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Röberga, Röberga, Ög</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>556155</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6432477</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Oppeby</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Linnea Druid</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Linnea Druid</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135474938</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135741743</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Röberga, Ög</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>556056</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6432617</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Oppeby</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg, Hugo Axelsson, Hasse Andersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135741743</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136038288</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80062</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Röberga, Ög</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>556139</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6432489</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Oppeby</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136038288</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136038211</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57979</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Röberga, Ög</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>556133</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6432506</v>
+      </c>
+      <c r="S13" t="n">
+        <v>50</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Oppeby</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136038211</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>136038298</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57979</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Röberga, Ög</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>556139</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6432489</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Oppeby</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136038298</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135742592</v>
+      </c>
+      <c r="B15" t="n">
+        <v>5497</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Röberga, Ög</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>555977</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6432526</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Oppeby</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg, Hugo Axelsson, Hasse Andersson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135742592</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>136038703</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58143</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Röberga, Ög</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>555996</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6432641</v>
+      </c>
+      <c r="S16" t="n">
+        <v>50</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Oppeby</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136038703</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135742534</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98297</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>219815</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Ekbräken</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Gymnocarpium dryopteris</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Newman</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Röberga, Röberga, Ög</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>555984</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6432565</v>
+      </c>
+      <c r="S17" t="n">
+        <v>28</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Oppeby</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Hasse Andersson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Hasse Andersson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135742534</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135742392</v>
+      </c>
+      <c r="B18" t="n">
+        <v>106413</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Röberga, Röberga, Ög</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>556022</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6432559</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Oppeby</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Hasse Andersson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Hasse Andersson, Rebecca Wikström, Hugo Axelsson, Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135742392</t>
         </is>
@@ -1463,6 +2496,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30317-2026 artfynd.xlsx
+++ b/artfynd/A 30317-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ18"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135474938</v>
+        <v>136075610</v>
       </c>
       <c r="B10" t="n">
-        <v>80060</v>
+        <v>92022</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1534,37 +1534,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>5445</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Röberga, Röberga, Ög</t>
+          <t>Röberga/Björkern, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>556155</v>
+        <v>555963</v>
       </c>
       <c r="R10" t="n">
-        <v>6432477</v>
+        <v>6432623</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1588,22 +1591,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>12:06</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>12:06</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1612,30 +1605,31 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Linnea Druid</t>
+          <t>Madeleine Askelöf</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Linnea Druid</t>
+          <t>Madeleine Askelöf</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135474938</t>
+          <t>https://artportalen.se/Sighting/136075610</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135741743</v>
+        <v>135474938</v>
       </c>
       <c r="B11" t="n">
         <v>80060</v>
@@ -1666,17 +1660,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Röberga, Ög</t>
+          <t>Röberga, Röberga, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>556056</v>
+        <v>556155</v>
       </c>
       <c r="R11" t="n">
-        <v>6432617</v>
+        <v>6432477</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1700,12 +1694,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1720,27 +1724,27 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Linnea Druid</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Hugo Axelsson, Hasse Andersson</t>
+          <t>Linnea Druid</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135741743</t>
+          <t>https://artportalen.se/Sighting/135474938</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136038288</v>
+        <v>135741743</v>
       </c>
       <c r="B12" t="n">
-        <v>80062</v>
+        <v>80060</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1772,13 +1776,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>556139</v>
+        <v>556056</v>
       </c>
       <c r="R12" t="n">
-        <v>6432489</v>
+        <v>6432617</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1802,12 +1806,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1827,65 +1831,60 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Emma Nordenberg, Hugo Axelsson, Hasse Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136038288</t>
+          <t>https://artportalen.se/Sighting/135741743</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>136038211</v>
+        <v>136038288</v>
       </c>
       <c r="B13" t="n">
-        <v>57979</v>
+        <v>80062</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Röberga, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>556133</v>
+        <v>556139</v>
       </c>
       <c r="R13" t="n">
-        <v>6432506</v>
+        <v>6432489</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1940,13 +1939,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136038211</t>
+          <t>https://artportalen.se/Sighting/136038288</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>136038298</v>
+        <v>136038211</v>
       </c>
       <c r="B14" t="n">
         <v>57979</v>
@@ -1975,27 +1974,24 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Röberga, Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>556139</v>
+        <v>556133</v>
       </c>
       <c r="R14" t="n">
-        <v>6432489</v>
+        <v>6432506</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2050,51 +2046,59 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136038298</t>
+          <t>https://artportalen.se/Sighting/136038211</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135742592</v>
+        <v>136038298</v>
       </c>
       <c r="B15" t="n">
-        <v>5497</v>
+        <v>57979</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>101410</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Röberga, Ög</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>555977</v>
+        <v>556139</v>
       </c>
       <c r="R15" t="n">
-        <v>6432526</v>
+        <v>6432489</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2121,12 +2125,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2146,60 +2150,68 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Hugo Axelsson, Hasse Andersson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135742592</t>
+          <t>https://artportalen.se/Sighting/136038298</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>136038703</v>
+        <v>136075757</v>
       </c>
       <c r="B16" t="n">
-        <v>58143</v>
+        <v>57979</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Röberga, Ög</t>
+          <t>Röberga/Björkern, Ög</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>555996</v>
+        <v>555966</v>
       </c>
       <c r="R16" t="n">
-        <v>6432641</v>
+        <v>6432630</v>
       </c>
       <c r="S16" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2229,6 +2241,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Spår av födosök på trädstam</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2243,27 +2260,27 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Madeleine Askelöf</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Madeleine Askelöf</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136038703</t>
+          <t>https://artportalen.se/Sighting/136075757</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135742534</v>
+        <v>136075891</v>
       </c>
       <c r="B17" t="n">
-        <v>98297</v>
+        <v>57979</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2271,37 +2288,45 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219815</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Röberga, Röberga, Ög</t>
+          <t>Röberga/Björkern, Ög</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>555984</v>
+        <v>556011</v>
       </c>
       <c r="R17" t="n">
-        <v>6432565</v>
+        <v>6432638</v>
       </c>
       <c r="S17" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2325,22 +2350,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>14:39</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>14:39</t>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Spår av födosök på trädstam</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2355,27 +2375,27 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Hasse Andersson</t>
+          <t>Madeleine Askelöf</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Hasse Andersson</t>
+          <t>Madeleine Askelöf</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135742534</t>
+          <t>https://artportalen.se/Sighting/136075891</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135742392</v>
+        <v>136075910</v>
       </c>
       <c r="B18" t="n">
-        <v>106413</v>
+        <v>57979</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2383,41 +2403,45 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Röberga, Röberga, Ög</t>
+          <t>Röberga/Björkern, Ög</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>556022</v>
+        <v>556058</v>
       </c>
       <c r="R18" t="n">
-        <v>6432559</v>
+        <v>6432631</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2441,22 +2465,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>14:35</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>14:35</t>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Spår av födosök på trädstam</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2465,23 +2484,570 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Hasse Andersson</t>
+          <t>Madeleine Askelöf</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Hasse Andersson, Rebecca Wikström, Hugo Axelsson, Emma Nordenberg</t>
+          <t>Madeleine Askelöf</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136075910</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135742592</v>
+      </c>
+      <c r="B19" t="n">
+        <v>5497</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Röberga, Ög</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>555977</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6432526</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Oppeby</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg, Hugo Axelsson, Hasse Andersson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135742592</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>136038703</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58143</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Röberga, Ög</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>555996</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6432641</v>
+      </c>
+      <c r="S20" t="n">
+        <v>50</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Oppeby</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136038703</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>136075867</v>
+      </c>
+      <c r="B21" t="n">
+        <v>58143</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Röberga/Björkern, Ög</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>555951</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6432576</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Oppeby</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Upprepad sång på flera platser från minst en individ.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Madeleine Askelöf</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Madeleine Askelöf</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136075867</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135742534</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98297</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>219815</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Ekbräken</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Gymnocarpium dryopteris</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Newman</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Röberga, Röberga, Ög</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>555984</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6432565</v>
+      </c>
+      <c r="S22" t="n">
+        <v>28</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Oppeby</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Hasse Andersson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Hasse Andersson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135742534</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135742392</v>
+      </c>
+      <c r="B23" t="n">
+        <v>106413</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Röberga, Röberga, Ög</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>556022</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6432559</v>
+      </c>
+      <c r="S23" t="n">
+        <v>15</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Oppeby</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Hasse Andersson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Hasse Andersson, Rebecca Wikström, Hugo Axelsson, Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135742392</t>
         </is>
@@ -2506,6 +3072,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30317-2026 artfynd.xlsx
+++ b/artfynd/A 30317-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136037267</v>
       </c>
       <c r="B2" t="n">
-        <v>97529</v>
+        <v>97530</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136037315</v>
       </c>
       <c r="B3" t="n">
-        <v>97529</v>
+        <v>97530</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135473483</v>
       </c>
       <c r="B4" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>136037006</v>
       </c>
       <c r="B7" t="n">
-        <v>96595</v>
+        <v>96596</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>135741780</v>
       </c>
       <c r="B8" t="n">
-        <v>92461</v>
+        <v>92475</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>135474938</v>
       </c>
       <c r="B11" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         <v>135741743</v>
       </c>
       <c r="B12" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>135742592</v>
       </c>
       <c r="B19" t="n">
-        <v>5497</v>
+        <v>5498</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>135742534</v>
       </c>
       <c r="B22" t="n">
-        <v>98297</v>
+        <v>98314</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>135742392</v>
       </c>
       <c r="B23" t="n">
-        <v>106413</v>
+        <v>106433</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 30317-2026 artfynd.xlsx
+++ b/artfynd/A 30317-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136037267</v>
       </c>
       <c r="B2" t="n">
-        <v>97530</v>
+        <v>97531</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136037315</v>
       </c>
       <c r="B3" t="n">
-        <v>97530</v>
+        <v>97531</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136037172</v>
       </c>
       <c r="B5" t="n">
-        <v>79637</v>
+        <v>79638</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>136037509</v>
       </c>
       <c r="B6" t="n">
-        <v>79637</v>
+        <v>79638</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>136037006</v>
       </c>
       <c r="B7" t="n">
-        <v>96596</v>
+        <v>96597</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>135741780</v>
       </c>
       <c r="B8" t="n">
-        <v>92475</v>
+        <v>92476</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>136038484</v>
       </c>
       <c r="B9" t="n">
-        <v>92022</v>
+        <v>92023</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>136075610</v>
       </c>
       <c r="B10" t="n">
-        <v>92022</v>
+        <v>92023</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         <v>135741743</v>
       </c>
       <c r="B12" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>136038288</v>
       </c>
       <c r="B13" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>135742534</v>
       </c>
       <c r="B22" t="n">
-        <v>98314</v>
+        <v>98315</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>135742392</v>
       </c>
       <c r="B23" t="n">
-        <v>106433</v>
+        <v>106435</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 30317-2026 artfynd.xlsx
+++ b/artfynd/A 30317-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136037267</v>
       </c>
       <c r="B2" t="n">
-        <v>97531</v>
+        <v>97532</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136037315</v>
       </c>
       <c r="B3" t="n">
-        <v>97531</v>
+        <v>97532</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>136037006</v>
       </c>
       <c r="B7" t="n">
-        <v>96597</v>
+        <v>96598</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>135741780</v>
       </c>
       <c r="B8" t="n">
-        <v>92476</v>
+        <v>92477</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>136038484</v>
       </c>
       <c r="B9" t="n">
-        <v>92023</v>
+        <v>92024</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>136075610</v>
       </c>
       <c r="B10" t="n">
-        <v>92023</v>
+        <v>92024</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>135742534</v>
       </c>
       <c r="B22" t="n">
-        <v>98315</v>
+        <v>98316</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>135742392</v>
       </c>
       <c r="B23" t="n">
-        <v>106435</v>
+        <v>106436</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 30317-2026 artfynd.xlsx
+++ b/artfynd/A 30317-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136037267</v>
       </c>
       <c r="B2" t="n">
-        <v>97532</v>
+        <v>97533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136037315</v>
       </c>
       <c r="B3" t="n">
-        <v>97532</v>
+        <v>97533</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136037172</v>
       </c>
       <c r="B5" t="n">
-        <v>79638</v>
+        <v>79639</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>136037509</v>
       </c>
       <c r="B6" t="n">
-        <v>79638</v>
+        <v>79639</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>136037006</v>
       </c>
       <c r="B7" t="n">
-        <v>96598</v>
+        <v>96599</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>135741780</v>
       </c>
       <c r="B8" t="n">
-        <v>92477</v>
+        <v>92478</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>136038484</v>
       </c>
       <c r="B9" t="n">
-        <v>92024</v>
+        <v>92025</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>136075610</v>
       </c>
       <c r="B10" t="n">
-        <v>92024</v>
+        <v>92025</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         <v>135741743</v>
       </c>
       <c r="B12" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>136038288</v>
       </c>
       <c r="B13" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>136038211</v>
       </c>
       <c r="B14" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>136038298</v>
       </c>
       <c r="B15" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>136075757</v>
       </c>
       <c r="B16" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>136075891</v>
       </c>
       <c r="B17" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>136075910</v>
       </c>
       <c r="B18" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2612,7 +2612,7 @@
         <v>136038703</v>
       </c>
       <c r="B20" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>136075867</v>
       </c>
       <c r="B21" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>135742534</v>
       </c>
       <c r="B22" t="n">
-        <v>98316</v>
+        <v>98317</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>135742392</v>
       </c>
       <c r="B23" t="n">
-        <v>106436</v>
+        <v>106437</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 30317-2026 artfynd.xlsx
+++ b/artfynd/A 30317-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136037267</v>
       </c>
       <c r="B2" t="n">
-        <v>97533</v>
+        <v>97539</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136037315</v>
       </c>
       <c r="B3" t="n">
-        <v>97533</v>
+        <v>97539</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136037172</v>
       </c>
       <c r="B5" t="n">
-        <v>79639</v>
+        <v>79643</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>136037509</v>
       </c>
       <c r="B6" t="n">
-        <v>79639</v>
+        <v>79643</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>136037006</v>
       </c>
       <c r="B7" t="n">
-        <v>96599</v>
+        <v>96605</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>135741780</v>
       </c>
       <c r="B8" t="n">
-        <v>92478</v>
+        <v>92484</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>136038484</v>
       </c>
       <c r="B9" t="n">
-        <v>92025</v>
+        <v>92031</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>136075610</v>
       </c>
       <c r="B10" t="n">
-        <v>92025</v>
+        <v>92031</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         <v>135741743</v>
       </c>
       <c r="B12" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>136038288</v>
       </c>
       <c r="B13" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>136038211</v>
       </c>
       <c r="B14" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>136038298</v>
       </c>
       <c r="B15" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>136075757</v>
       </c>
       <c r="B16" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>136075891</v>
       </c>
       <c r="B17" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>136075910</v>
       </c>
       <c r="B18" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2612,7 +2612,7 @@
         <v>136038703</v>
       </c>
       <c r="B20" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>136075867</v>
       </c>
       <c r="B21" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>135742534</v>
       </c>
       <c r="B22" t="n">
-        <v>98317</v>
+        <v>98323</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>135742392</v>
       </c>
       <c r="B23" t="n">
-        <v>106437</v>
+        <v>106443</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 30317-2026 artfynd.xlsx
+++ b/artfynd/A 30317-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136037267</v>
       </c>
       <c r="B2" t="n">
-        <v>97539</v>
+        <v>97540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136037315</v>
       </c>
       <c r="B3" t="n">
-        <v>97539</v>
+        <v>97540</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136037172</v>
       </c>
       <c r="B5" t="n">
-        <v>79643</v>
+        <v>79644</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>136037509</v>
       </c>
       <c r="B6" t="n">
-        <v>79643</v>
+        <v>79644</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>136037006</v>
       </c>
       <c r="B7" t="n">
-        <v>96605</v>
+        <v>96606</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>135741780</v>
       </c>
       <c r="B8" t="n">
-        <v>92484</v>
+        <v>92485</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>136038484</v>
       </c>
       <c r="B9" t="n">
-        <v>92031</v>
+        <v>92032</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>136075610</v>
       </c>
       <c r="B10" t="n">
-        <v>92031</v>
+        <v>92032</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         <v>135741743</v>
       </c>
       <c r="B12" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>136038288</v>
       </c>
       <c r="B13" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>136038211</v>
       </c>
       <c r="B14" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>136038298</v>
       </c>
       <c r="B15" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>136075757</v>
       </c>
       <c r="B16" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>136075891</v>
       </c>
       <c r="B17" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>136075910</v>
       </c>
       <c r="B18" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2612,7 +2612,7 @@
         <v>136038703</v>
       </c>
       <c r="B20" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>136075867</v>
       </c>
       <c r="B21" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>135742534</v>
       </c>
       <c r="B22" t="n">
-        <v>98323</v>
+        <v>98324</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>135742392</v>
       </c>
       <c r="B23" t="n">
-        <v>106443</v>
+        <v>106444</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 30317-2026 artfynd.xlsx
+++ b/artfynd/A 30317-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136037267</v>
       </c>
       <c r="B2" t="n">
-        <v>97540</v>
+        <v>97551</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136037315</v>
       </c>
       <c r="B3" t="n">
-        <v>97540</v>
+        <v>97551</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136037172</v>
       </c>
       <c r="B5" t="n">
-        <v>79644</v>
+        <v>79648</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>136037509</v>
       </c>
       <c r="B6" t="n">
-        <v>79644</v>
+        <v>79648</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>136037006</v>
       </c>
       <c r="B7" t="n">
-        <v>96606</v>
+        <v>96617</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>135741780</v>
       </c>
       <c r="B8" t="n">
-        <v>92485</v>
+        <v>92491</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>136038484</v>
       </c>
       <c r="B9" t="n">
-        <v>92032</v>
+        <v>92038</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>136075610</v>
       </c>
       <c r="B10" t="n">
-        <v>92032</v>
+        <v>92038</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         <v>135741743</v>
       </c>
       <c r="B12" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>136038288</v>
       </c>
       <c r="B13" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>135742534</v>
       </c>
       <c r="B22" t="n">
-        <v>98324</v>
+        <v>98335</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>135742392</v>
       </c>
       <c r="B23" t="n">
-        <v>106444</v>
+        <v>106455</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 30317-2026 artfynd.xlsx
+++ b/artfynd/A 30317-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136037267</v>
       </c>
       <c r="B2" t="n">
-        <v>97551</v>
+        <v>97564</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136037315</v>
       </c>
       <c r="B3" t="n">
-        <v>97551</v>
+        <v>97564</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136037172</v>
       </c>
       <c r="B5" t="n">
-        <v>79648</v>
+        <v>79654</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>136037509</v>
       </c>
       <c r="B6" t="n">
-        <v>79648</v>
+        <v>79654</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>136037006</v>
       </c>
       <c r="B7" t="n">
-        <v>96617</v>
+        <v>96630</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>135741780</v>
       </c>
       <c r="B8" t="n">
-        <v>92491</v>
+        <v>92498</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>136038484</v>
       </c>
       <c r="B9" t="n">
-        <v>92038</v>
+        <v>92045</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>136075610</v>
       </c>
       <c r="B10" t="n">
-        <v>92038</v>
+        <v>92045</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         <v>135741743</v>
       </c>
       <c r="B12" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>136038288</v>
       </c>
       <c r="B13" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>136038211</v>
       </c>
       <c r="B14" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>136038298</v>
       </c>
       <c r="B15" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>136075757</v>
       </c>
       <c r="B16" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>136075891</v>
       </c>
       <c r="B17" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>136075910</v>
       </c>
       <c r="B18" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2612,7 +2612,7 @@
         <v>136038703</v>
       </c>
       <c r="B20" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>136075867</v>
       </c>
       <c r="B21" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>135742534</v>
       </c>
       <c r="B22" t="n">
-        <v>98335</v>
+        <v>98348</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>135742392</v>
       </c>
       <c r="B23" t="n">
-        <v>106455</v>
+        <v>106468</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 30317-2026 artfynd.xlsx
+++ b/artfynd/A 30317-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136037267</v>
       </c>
       <c r="B2" t="n">
-        <v>97564</v>
+        <v>97565</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136037315</v>
       </c>
       <c r="B3" t="n">
-        <v>97564</v>
+        <v>97565</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>136037006</v>
       </c>
       <c r="B7" t="n">
-        <v>96630</v>
+        <v>96631</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>135741780</v>
       </c>
       <c r="B8" t="n">
-        <v>92498</v>
+        <v>92499</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>136038484</v>
       </c>
       <c r="B9" t="n">
-        <v>92045</v>
+        <v>92046</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>136075610</v>
       </c>
       <c r="B10" t="n">
-        <v>92045</v>
+        <v>92046</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 30317-2026 artfynd.xlsx
+++ b/artfynd/A 30317-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136037267</v>
       </c>
       <c r="B2" t="n">
-        <v>97565</v>
+        <v>97578</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136037315</v>
       </c>
       <c r="B3" t="n">
-        <v>97565</v>
+        <v>97578</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136037172</v>
       </c>
       <c r="B5" t="n">
-        <v>79654</v>
+        <v>79667</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>136037509</v>
       </c>
       <c r="B6" t="n">
-        <v>79654</v>
+        <v>79667</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>136037006</v>
       </c>
       <c r="B7" t="n">
-        <v>96631</v>
+        <v>96644</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>136038484</v>
       </c>
       <c r="B9" t="n">
-        <v>92046</v>
+        <v>92059</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>136075610</v>
       </c>
       <c r="B10" t="n">
-        <v>92046</v>
+        <v>92059</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>136038288</v>
       </c>
       <c r="B13" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>136038211</v>
       </c>
       <c r="B14" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>136038298</v>
       </c>
       <c r="B15" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>136075757</v>
       </c>
       <c r="B16" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>136075891</v>
       </c>
       <c r="B17" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>136075910</v>
       </c>
       <c r="B18" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2612,7 +2612,7 @@
         <v>136038703</v>
       </c>
       <c r="B20" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>136075867</v>
       </c>
       <c r="B21" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 30317-2026 artfynd.xlsx
+++ b/artfynd/A 30317-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136037267</v>
       </c>
       <c r="B2" t="n">
-        <v>97578</v>
+        <v>97579</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136037315</v>
       </c>
       <c r="B3" t="n">
-        <v>97578</v>
+        <v>97579</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136037172</v>
       </c>
       <c r="B5" t="n">
-        <v>79667</v>
+        <v>79668</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>136037509</v>
       </c>
       <c r="B6" t="n">
-        <v>79667</v>
+        <v>79668</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>136037006</v>
       </c>
       <c r="B7" t="n">
-        <v>96644</v>
+        <v>96645</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>136038484</v>
       </c>
       <c r="B9" t="n">
-        <v>92059</v>
+        <v>92060</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>136075610</v>
       </c>
       <c r="B10" t="n">
-        <v>92059</v>
+        <v>92060</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>136038288</v>
       </c>
       <c r="B13" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
